--- a/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
@@ -643,7 +643,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -739,7 +739,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -931,7 +931,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-24</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8864,7 +8864,7 @@
           <t>A | 1012呎 (3房)
 $4100万
 $40,514/呎
-(已售)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8888,7 +8888,7 @@
           <t>D | 406呎 (1房)
 $993万
 $24,458/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -8909,7 +8909,7 @@
           <t>A | 1012呎 (3房)
 $3196万
 $31,581/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -8917,7 +8917,7 @@
           <t>B | 821呎 (3房)
 $2545万
 $31,000/呎
-(已售)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8925,7 +8925,7 @@
           <t>C | 979呎 (3房)
 $3084万
 $31,499/呎
-(已售)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -8933,7 +8933,7 @@
           <t>D | 406呎 (1房)
 $986万
 $24,286/呎
-(已售)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr"/>
@@ -8954,7 +8954,7 @@
           <t>A | 1012呎 (3房)
 $3340万
 $33,000/呎
-(已售)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8978,7 +8978,7 @@
           <t>D | 406呎 (1房)
 $978万
 $24,089/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
           <t>A | 1012呎 (3房)
 $3137万
 $31,000/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>C | 979呎 (3房)
 $3024万
 $30,888/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -9023,7 +9023,7 @@
           <t>D | 406呎 (1房)
 $971万
 $23,916/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
           <t>A | 1012呎 (3房)
 $3076万
 $30,400/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9052,7 +9052,7 @@
           <t>B | 821呎 (3房)
 $2482万
 $30,231/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -9060,7 +9060,7 @@
           <t>C | 978呎 (3房)
 $2980万
 $30,470/呎
-(已售)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -9068,7 +9068,7 @@
           <t>D | 406呎 (1房)
 $964万
 $23,744/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
           <t>A | 1012呎 (3房)
 $3066万
 $30,300/呎
-(已售)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9097,7 +9097,7 @@
           <t>B | 821呎 (3房)
 $2459万
 $29,946/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -9113,7 +9113,7 @@
           <t>D | 406呎 (1房)
 $957万
 $23,571/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -9134,7 +9134,7 @@
           <t>A | 524呎 (2房)
 $1479万
 $28,221/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9142,7 +9142,7 @@
           <t>B | 386呎 (1房)
 $1065万
 $27,601/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9150,7 +9150,7 @@
           <t>C | 382呎 (1房)
 $1005万
 $26,309/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9158,7 +9158,7 @@
           <t>D | 297呎 (开放式)
 $795万
 $26,771/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -9166,7 +9166,7 @@
           <t>E | 220呎 (开放式)
 $501万
 $22,773/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -9174,7 +9174,7 @@
           <t>F | 293呎 (开放式)
 $628万
 $21,447/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -9182,7 +9182,7 @@
           <t>G | 266呎 (开放式)
 $541万
 $20,342/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -9190,7 +9190,7 @@
           <t>H | 252呎 (开放式)
 $512万
 $20,337/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -9198,7 +9198,7 @@
           <t>J | 211呎 (开放式)
 $430万
 $20,393/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -9206,7 +9206,7 @@
           <t>K | 370呎 (1房)
 $862万
 $23,297/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
           <t>A | 524呎 (2房)
 $1483万
 $28,303/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9229,7 +9229,7 @@
           <t>B | 386呎 (1房)
 $1068万
 $27,666/呎
-(已售)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9237,7 +9237,7 @@
           <t>C | 382呎 (1房)
 $1007万
 $26,366/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9245,7 +9245,7 @@
           <t>D | 297呎 (开放式)
 $789万
 $26,566/呎
-(已售)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -9253,7 +9253,7 @@
           <t>E | 220呎 (开放式)
 $507万
 $23,045/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -9261,7 +9261,7 @@
           <t>F | 293呎 (开放式)
 $630万
 $21,509/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -9269,7 +9269,7 @@
           <t>G | 266呎 (开放式)
 $538万
 $20,211/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -9277,7 +9277,7 @@
           <t>H | 252呎 (开放式)
 $509万
 $20,202/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -9285,7 +9285,7 @@
           <t>J | 211呎 (开放式)
 $427万
 $20,227/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -9293,7 +9293,7 @@
           <t>K | 370呎 (1房)
 $856万
 $23,135/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
           <t>A | 524呎 (2房)
 $1457万
 $27,802/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9316,7 +9316,7 @@
           <t>B | 386呎 (1房)
 $1053万
 $27,272/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -9324,7 +9324,7 @@
           <t>C | 382呎 (1房)
 $990万
 $25,921/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -9332,7 +9332,7 @@
           <t>D | 297呎 (开放式)
 $804万
 $27,067/呎
-(已售)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -9340,7 +9340,7 @@
           <t>E | 220呎 (开放式)
 $516万
 $23,455/呎
-(已售)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -9348,7 +9348,7 @@
           <t>F | 294呎 (开放式)
 $626万
 $21,286/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -9356,7 +9356,7 @@
           <t>G | 266呎 (开放式)
 $533万
 $20,049/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -9364,7 +9364,7 @@
           <t>H | 252呎 (开放式)
 $506万
 $20,063/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -9372,7 +9372,7 @@
           <t>J | 211呎 (开放式)
 $428万
 $20,265/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>K | 370呎 (1房)
 $866万
 $23,405/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
           <t>A | 524呎 (2房)
 $1461万
 $27,884/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9403,7 +9403,7 @@
           <t>B | 386呎 (1房)
 $1050万
 $27,207/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9411,7 +9411,7 @@
           <t>C | 382呎 (1房)
 $982万
 $25,712/呎
-(已售)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -9419,7 +9419,7 @@
           <t>D | 297呎 (开放式)
 $777万
 $26,162/呎
-(已售)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -9427,7 +9427,7 @@
           <t>E | 220呎 (开放式)
 $500万
 $22,718/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -9435,7 +9435,7 @@
           <t>F | 293呎 (开放式)
 $621万
 $21,201/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>G | 266呎 (开放式)
 $530万
 $19,917/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -9451,7 +9451,7 @@
           <t>H | 252呎 (开放式)
 $501万
 $19,889/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -9459,7 +9459,7 @@
           <t>J | 211呎 (开放式)
 $420万
 $19,900/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -9467,7 +9467,7 @@
           <t>K | 370呎 (1房)
 $843万
 $22,784/呎
-(已售)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
           <t>A | 524呎 (2房)
 $1435万
 $27,384/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9490,7 +9490,7 @@
           <t>B | 386呎 (1房)
 $1033万
 $26,762/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -9498,7 +9498,7 @@
           <t>C | 382呎 (1房)
 $975万
 $25,531/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>D | 297呎 (开放式)
 $763万
 $25,690/呎
-(已售)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>E | 220呎 (开放式)
 $491万
 $22,309/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -9522,7 +9522,7 @@
           <t>F | 293呎 (开放式)
 $617万
 $21,051/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -9530,7 +9530,7 @@
           <t>G | 266呎 (开放式)
 $526万
 $19,756/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -9538,7 +9538,7 @@
           <t>H | 252呎 (开放式)
 $498万
 $19,754/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -9546,7 +9546,7 @@
           <t>J | 211呎 (开放式)
 $417万
 $19,782/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -9554,7 +9554,7 @@
           <t>K | 370呎 (1房)
 $836万
 $22,595/呎
-(已售)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
           <t>A | 524呎 (2房)
 $1424万
 $27,185/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>B | 386呎 (1房)
 $1024万
 $26,526/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9585,7 +9585,7 @@
           <t>C | 382呎 (1房)
 $968万
 $25,348/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -9593,7 +9593,7 @@
           <t>D | 297呎 (开放式)
 $757万
 $25,488/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>E | 220呎 (开放式)
 $488万
 $22,173/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -9609,7 +9609,7 @@
           <t>F | 294呎 (开放式)
 $605万
 $20,588/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -9617,7 +9617,7 @@
           <t>G | 266呎 (开放式)
 $521万
 $19,590/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -9625,7 +9625,7 @@
           <t>H | 252呎 (开放式)
 $494万
 $19,611/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -9633,7 +9633,7 @@
           <t>J | 211呎 (开放式)
 $414万
 $19,611/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -9641,7 +9641,7 @@
           <t>K | 370呎 (1房)
 $830万
 $22,432/呎
-(已售)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
           <t>A | 524呎 (2房)
 $1414万
 $26,985/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -9664,7 +9664,7 @@
           <t>B | 386呎 (1房)
 $1017万
 $26,337/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -9672,7 +9672,7 @@
           <t>C | 382呎 (1房)
 $960万
 $25,141/呎
-(已售)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -9680,7 +9680,7 @@
           <t>D | 297呎 (开放式)
 $752万
 $25,320/呎
-(已售)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -9688,7 +9688,7 @@
           <t>E | 220呎 (开放式)
 $479万
 $21,773/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -9696,7 +9696,7 @@
           <t>F | 293呎 (开放式)
 $601万
 $20,505/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -9704,7 +9704,7 @@
           <t>G | 266呎 (开放式)
 $518万
 $19,459/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -9712,7 +9712,7 @@
           <t>H | 252呎 (开放式)
 $495万
 $19,639/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -9720,7 +9720,7 @@
           <t>J | 211呎 (开放式)
 $411万
 $19,488/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -9728,7 +9728,7 @@
           <t>K | 370呎 (1房)
 $824万
 $22,270/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
           <t>A | 524呎 (2房)
 $1418万
 $27,057/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9751,7 +9751,7 @@
           <t>B | 386呎 (1房)
 $1008万
 $26,122/呎
-(已售)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9759,7 +9759,7 @@
           <t>C | 382呎 (1房)
 $954万
 $24,961/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -9767,7 +9767,7 @@
           <t>D | 297呎 (开放式)
 $752万
 $25,320/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -9775,7 +9775,7 @@
           <t>E | 220呎 (开放式)
 $475万
 $21,591/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -9783,7 +9783,7 @@
           <t>F | 293呎 (开放式)
 $596万
 $20,355/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -9791,7 +9791,7 @@
           <t>G | 266呎 (开放式)
 $514万
 $19,331/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -9799,7 +9799,7 @@
           <t>H | 252呎 (开放式)
 $486万
 $19,306/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -9807,7 +9807,7 @@
           <t>J | 211呎 (开放式)
 $408万
 $19,332/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -9815,7 +9815,7 @@
           <t>K | 370呎 (1房)
 $838万
 $22,657/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
           <t>A | 524呎 (2房)
 $1393万
 $26,586/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9838,7 +9838,7 @@
           <t>B | 385呎 (1房)
 $1003万
 $26,047/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -9846,7 +9846,7 @@
           <t>C | 382呎 (1房)
 $946万
 $24,777/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -9854,7 +9854,7 @@
           <t>D | 297呎 (开放式)
 $746万
 $25,118/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -9862,7 +9862,7 @@
           <t>E | 220呎 (开放式)
 $472万
 $21,455/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -9870,7 +9870,7 @@
           <t>F | 293呎 (开放式)
 $592万
 $20,201/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -9878,7 +9878,7 @@
           <t>G | 266呎 (开放式)
 $510万
 $19,165/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -9886,7 +9886,7 @@
           <t>H | 252呎 (开放式)
 $483万
 $19,163/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -9894,7 +9894,7 @@
           <t>J | 211呎 (开放式)
 $405万
 $19,204/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -9902,7 +9902,7 @@
           <t>K | 370呎 (1房)
 $827万
 $22,359/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
           <t>A | 524呎 (2房)
 $1362万
 $25,989/呎
-(已售)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9925,7 +9925,7 @@
           <t>B | 385呎 (1房)
 $1000万
 $25,969/呎
-(已售)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9933,7 +9933,7 @@
           <t>C | 382呎 (1房)
 $926万
 $24,233/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -9941,7 +9941,7 @@
           <t>D | 297呎 (开放式)
 $731万
 $24,626/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -9949,7 +9949,7 @@
           <t>E | 220呎 (开放式)
 $468万
 $21,273/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -9957,7 +9957,7 @@
           <t>F | 294呎 (开放式)
 $588万
 $19,983/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -9965,7 +9965,7 @@
           <t>G | 266呎 (开放式)
 $506万
 $19,038/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -9973,7 +9973,7 @@
           <t>H | 252呎 (开放式)
 $484万
 $19,218/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -9981,7 +9981,7 @@
           <t>J | 211呎 (开放式)
 $402万
 $19,038/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>K | 370呎 (1房)
 $813万
 $21,978/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
           <t>A | 524呎 (2房)
 $1351万
 $25,790/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10012,7 +10012,7 @@
           <t>B | 386呎 (1房)
 $976万
 $25,298/呎
-(已售)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -10020,7 +10020,7 @@
           <t>C | 382呎 (1房)
 $919万
 $24,050/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -10028,7 +10028,7 @@
           <t>D | 297呎 (开放式)
 $724万
 $24,377/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -10036,7 +10036,7 @@
           <t>E | 220呎 (开放式)
 $465万
 $21,136/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -10044,7 +10044,7 @@
           <t>F | 293呎 (开放式)
 $583万
 $19,898/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -10052,7 +10052,7 @@
           <t>G | 266呎 (开放式)
 $502万
 $18,872/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -10060,7 +10060,7 @@
           <t>H | 252呎 (开放式)
 $476万
 $18,889/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -10068,7 +10068,7 @@
           <t>J | 211呎 (开放式)
 $398万
 $18,882/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -10076,7 +10076,7 @@
           <t>K | 370呎 (1房)
 $819万
 $22,141/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
           <t>A | 524呎 (2房)
 $1341万
 $25,590/呎
-(已售)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10099,7 +10099,7 @@
           <t>B | 385呎 (1房)
 $965万
 $25,070/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10107,7 +10107,7 @@
           <t>C | 382呎 (1房)
 $912万
 $23,872/呎
-(已售)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -10115,7 +10115,7 @@
           <t>D | 297呎 (开放式)
 $713万
 $24,007/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -10123,7 +10123,7 @@
           <t>E | 220呎 (开放式)
 $461万
 $20,955/呎
-(已售)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -10131,7 +10131,7 @@
           <t>F | 293呎 (开放式)
 $579万
 $19,747/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -10139,7 +10139,7 @@
           <t>G | 266呎 (开放式)
 $504万
 $18,932/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -10147,7 +10147,7 @@
           <t>H | 252呎 (开放式)
 $472万
 $18,750/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -10155,7 +10155,7 @@
           <t>J | 211呎 (开放式)
 $400万
 $18,943/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -10163,7 +10163,7 @@
           <t>K | 370呎 (1房)
 $801万
 $21,651/呎
-(已售)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
           <t>A | 524呎 (2房)
 $1312万
 $25,032/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -10186,7 +10186,7 @@
           <t>B | 385呎 (1房)
 $943万
 $24,499/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -10194,7 +10194,7 @@
           <t>C | 382呎 (1房)
 $891万
 $23,322/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -10202,7 +10202,7 @@
           <t>D | 297呎 (开放式)
 $696万
 $23,434/呎
-(已售)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -10210,7 +10210,7 @@
           <t>E | 220呎 (开放式)
 $458万
 $20,818/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -10218,7 +10218,7 @@
           <t>F | 293呎 (开放式)
 $575万
 $19,628/呎
-(已售)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -10226,7 +10226,7 @@
           <t>G | 266呎 (开放式)
 $495万
 $18,613/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -10234,7 +10234,7 @@
           <t>H | 252呎 (开放式)
 $469万
 $18,615/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -10242,7 +10242,7 @@
           <t>J | 211呎 (开放式)
 $393万
 $18,630/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -10250,7 +10250,7 @@
           <t>K | 370呎 (1房)
 $795万
 $21,486/呎
-(已售)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
           <t>A | 524呎 (2房)
 $1304万
 $24,893/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10273,7 +10273,7 @@
           <t>B | 385呎 (1房)
 $939万
 $24,392/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10281,7 +10281,7 @@
           <t>C | 382呎 (1房)
 $887万
 $23,220/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -10289,7 +10289,7 @@
           <t>D | 297呎 (开放式)
 $693万
 $23,333/呎
-(已售)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -10297,7 +10297,7 @@
           <t>E | 220呎 (开放式)
 $455万
 $20,682/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -10305,7 +10305,7 @@
           <t>F | 293呎 (开放式)
 $571万
 $19,502/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -10313,7 +10313,7 @@
           <t>G | 266呎 (开放式)
 $492万
 $18,515/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -10321,7 +10321,7 @@
           <t>H | 252呎 (开放式)
 $471万
 $18,698/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -10329,7 +10329,7 @@
           <t>J | 211呎 (开放式)
 $394万
 $18,697/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -10337,7 +10337,7 @@
           <t>K | 370呎 (1房)
 $791万
 $21,378/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
           <t>B | 375呎 (1房)
 $886万
 $23,627/呎
-(已售)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -10368,7 +10368,7 @@
           <t>C | 369呎 (1房)
 $874万
 $23,686/呎
-(已售)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -10376,7 +10376,7 @@
           <t>D | 286呎 (开放式)
 $773万
 $27,031/呎
-(已售)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -10384,7 +10384,7 @@
           <t>E | 206呎 (开放式)
 $520万
 $25,243/呎
-(已售)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -10392,7 +10392,7 @@
           <t>F | 294呎 (开放式)
 $569万
 $19,350/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -10400,7 +10400,7 @@
           <t>G | 266呎 (开放式)
 $488万
 $18,353/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -10408,7 +10408,7 @@
           <t>H | 252呎 (开放式)
 $464万
 $18,405/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -10416,7 +10416,7 @@
           <t>J | 211呎 (开放式)
 $393万
 $18,611/呎
-(已售)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr"/>

--- a/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
@@ -204,61 +204,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
@@ -204,61 +204,61 @@
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -644,7 +644,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
